--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_270_Gambia.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_270_Gambia.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rd270a37dc4ce4441"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rd9d36c83cbd54182"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rf725a59b5eca4839"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rd32b67d5bc0d4c17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R7c6435f21a21462d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R41599566f5734012"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rc42d3f6934a94ca0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R4cb65aa6e29c497f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Ree4b6f7a007149cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R9417b6447dc340d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R150de750d5d34be1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R0677c8a417d04681"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ270CommercialTable" displayName="EEZ270CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ270CommercialTable" displayName="EEZ270CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ270FunctionalTable" displayName="EEZ270FunctionalTable" ref="A1:O26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O26"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ270FunctionalTable" displayName="EEZ270FunctionalTable" ref="A1:E26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E26"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ270ValidationTable" displayName="EEZ270ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ270ValidationTable" displayName="EEZ270ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -16640,7 +16594,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8122af89e5c448ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa935cea85ad4e7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16650,20 +16604,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -16671,660 +16615,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>330.53025248989996</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>330.53025248989996</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$239,A2,'Species'!$U$2:$U$239))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>42580.54495911319</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>42580.54495911319</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>47.280110348300006</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.496506047254794</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>3136.9388095901318</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>47.280110348300006</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>3143.1510996809634</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$239,A3,'Species'!$U$2:$U$239))</x:f>
-        <x:v>148608.53083429646</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.496506047254794</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>3136.9388095901318</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>148314.8130732863</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>293.7177610101644</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0019803669972265</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0019803669972265725</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>3031.8644578154</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.942492364694336</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>87.59763170097904</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>3031.8644578154</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>121.3239834935709</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$239,A4,'Species'!$U$2:$U$239))</x:f>
-        <x:v>367837.8734347399</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.942492364694336</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>87.59763170097904</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>265584.1461430019</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>102253.72729173797</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.3850144249072767</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.38501442490727655</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>961.3566620444001</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.2909391854113097</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>195.406580728569</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>961.3566620444001</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>200.37848511798896</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$239,A5,'Species'!$U$2:$U$239))</x:f>
-        <x:v>192635.19159854337</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.2909391854113097</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>195.406580728569</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>187855.4181907267</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>4779.773407816683</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0254438943196402</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.025443894319640295</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>82011.59552194811</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.9719937211330114</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>93.75484521034596</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>82011.59552194811</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>126.28585590550468</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$239,A6,'Species'!$U$2:$U$239))</x:f>
-        <x:v>10356904.534665272</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.9719937211330114</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>93.75484521034596</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>7688984.443613747</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>2667920.0910515245</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.3469795147351902</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.34697951473519023</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>3274.5586166909</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.2396876115591757</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>17.365512763886752</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>3274.5586166909</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>33.56466061724434</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$239,A7,'Species'!$U$2:$U$239))</x:f>
-        <x:v>109909.44864050318</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.2396876115591757</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>17.365512763886752</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>56864.38945424117</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>53045.059186262006</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.9328344099948074</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.9328344099948073</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>39452.395739515516</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.3763811356123345</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>237.8927110517679</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>39452.395739515516</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>314.50648465300145</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$239,A8,'Species'!$U$2:$U$239))</x:f>
-        <x:v>12408034.295174077</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.3763811356123345</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>237.8927110517679</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>9385437.379960563</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>3022596.915213514</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.3220517907526879</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.32205179075268786</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>36658.1141818274</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6008449742028943</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>398.8824918162568</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>36658.1141818274</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>664.5339644618643</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$239,A9,'Species'!$U$2:$U$239))</x:f>
-        <x:v>24360561.94694545</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6008449742028943</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>398.8824918162568</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>14622279.930132173</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>9738282.016813278</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.6659893028545825</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.6659893028545825</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>58.02314372409999</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.884873110046511</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>767.1373183337884</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>58.02314372409999</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>775.0408910371751</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$239,A10,'Species'!$U$2:$U$239))</x:f>
-        <x:v>44970.30901270453</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.884873110046511</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>767.1373183337884</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>44511.71887780205</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>458.5901349024789</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.010302683123998</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.010302683123998102</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1795.5860826402002</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.023988045784975</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1056.7884200808141</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1795.5860826402002</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1588.2519987363514</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$239,A11,'Species'!$U$2:$U$239))</x:f>
-        <x:v>2851843.1846564733</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.023988045784975</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1056.7884200808141</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1897554.5793924353</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>954288.6052640381</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.5029044305906527</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.5029044305906527</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>684.9980306893999</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.426599098237934</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2670.540067119765</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>684.9980306893999</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2677.0724236345554</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$239,A12,'Species'!$U$2:$U$239))</x:f>
-        <x:v>1833789.3382025694</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.426599098237934</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2670.540067119765</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>1829314.686854177</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>4474.651348392479</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.002446080699263</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.0024460806992630756</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc83eb7003174621"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24264e166a554012"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17334,20 +16849,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -17355,1416 +16860,497 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>3803.3967462379</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.7069790726964795</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>509.30632857422813</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>3803.3967462379</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>548.8465335472431</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$239,A2,'Species'!$U$2:$U$239))</x:f>
-        <x:v>2087481.119877535</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.7069790726964795</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>509.30632857422813</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1937094.03293759</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>150387.0869399449</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0776354087012925</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.07763540870129257</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.1831566107</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.374408073521967</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2368.14381719026</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.1831566107</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2439.0213837486326</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$239,A3,'Species'!$U$2:$U$239))</x:f>
-        <x:v>446.7228900722236</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.374408073521967</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2368.14381719026</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>433.74119520672843</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>12.981694865495172</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0299295870647192</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.029929587064719262</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.050977395</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.050977395</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$239,A4,'Species'!$U$2:$U$239))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>111.52638846991778</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>111.52638846991778</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1477.4424045121</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.33925253534485</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2183.9995037140757</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1477.4424045121</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2304.823848662606</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$239,A5,'Species'!$U$2:$U$239))</x:f>
-        <x:v>3405244.488944913</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.33925253534485</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2183.9995037140757</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>3226733.478220557</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>178511.01072435593</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0553225148371408</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.055322514837140874</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>4798.743878293999</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.910730549013898</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>814.1989706995116</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>4798.743878293999</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>839.3925334251019</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$239,A6,'Species'!$U$2:$U$239))</x:f>
-        <x:v>4028029.7812593984</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.910730549013898</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>814.1989706995116</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>3907132.3263575565</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>120897.45490184193</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0309427592421854</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.03094275924218548</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1573.8375100573</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.409856258746092</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2569.545183022057</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1573.8375100573</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2628.9260592061955</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$239,A7,'Species'!$U$2:$U$239))</x:f>
-        <x:v>4137502.443145829</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.409856258746092</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2569.545183022057</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>4044046.592827163</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>93455.85031866562</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0231094890163794</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.02310948901637934</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>272.6918458576</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.4901277449071406</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>309.12045565864355</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>272.6918458576</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>539.8665087324963</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$239,A8,'Species'!$U$2:$U$239))</x:f>
-        <x:v>147217.19478296256</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.4901277449071406</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>309.12045565864355</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>84294.62764589791</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>62922.567137064645</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.746459992698321</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.746459992698321</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>408.2125357692</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.5870812401218224</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>386.439258507271</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>408.2125357692</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>408.8754549842371</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$239,A9,'Species'!$U$2:$U$239))</x:f>
-        <x:v>166908.08629290079</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.5870812401218224</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>386.439258507271</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>157749.34963602247</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>9158.736656878318</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.058058791861966</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.05805879186196592</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>1401.1457646064002</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.146958978475501</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1402.6812072784705</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>1401.1457646064002</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1874.7735752898373</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$239,A10,'Species'!$U$2:$U$239))</x:f>
-        <x:v>2626831.0546133537</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.146958978475501</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1402.6812072784705</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1965360.832671221</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>661470.2219421326</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.336564263898093</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.33656426389809296</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1000.7814932409</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.3967036759255502</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>249.28932170768525</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1000.7814932409</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>254.70956117723702</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$239,A11,'Species'!$U$2:$U$239))</x:f>
-        <x:v>254908.61497768963</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.3967036759255502</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>249.28932170768525</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>249484.13962762835</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>5424.475350061286</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0217427663263792</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.02174276632637921</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>9.7744714422</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.480090306735993</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>3020.5797512677455</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>9.7744714422</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>3075.3645842689803</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$239,A12,'Species'!$U$2:$U$239))</x:f>
-        <x:v>30060.06330329042</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.480090306735993</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>3020.5797512677455</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>29524.570517654156</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>535.4927856362629</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0181371913713722</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.01813719137137206</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>4.4334199194</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.081535821583289</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1206.5236008665938</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>4.4334199194</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1207.4682948030031</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$239,A13,'Species'!$U$2:$U$239))</x:f>
-        <x:v>5353.213990223586</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.081535821583289</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1206.5236008665938</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>5349.025765308173</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>4.18822491541323</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0007829883607173</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.0007829883607172967</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>6803.2841659415</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.677388823605524</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>475.76098386537325</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>6803.2841659415</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>742.5738119193705</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$239,A14,'Species'!$U$2:$U$239))</x:f>
-        <x:v>5051940.656673875</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.677388823605524</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>475.76098386537325</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>3236737.1683040434</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>1815203.4883698313</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.560812754938933</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.560812754938933</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>42230.5803876816</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.3145356742278267</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>206.31731354681062</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>42230.5803876816</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>237.3590796191646</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$239,A15,'Species'!$U$2:$U$239))</x:f>
-        <x:v>10023811.692603247</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.3145356742278267</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>206.31731354681062</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>8712899.895109097</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>1310911.7974941507</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.1504564282013636</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.15045642820136365</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>52334.81279717849</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.9558043074930946</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>90.32423822144118</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>52334.81279717849</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>142.00201984528033</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$239,A16,'Species'!$U$2:$U$239))</x:f>
-        <x:v>7431649.125423971</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.9558043074930946</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>90.32423822144118</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>4727102.098366878</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>2704547.0270570926</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.5721363682818403</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.5721363682818404</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>5809.0589549816</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.6933410710783128</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>493.56126775155553</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>5809.0589549816</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>1087.2666725749964</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$239,A17,'Species'!$U$2:$U$239))</x:f>
-        <x:v>6315996.200774831</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.6933410710783128</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>493.56126775155553</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>2867126.502264245</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>3448869.698510586</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>2.202901126192696</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>1.202901126192696</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>3274.5590800539003</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.2396876384891278</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>17.36551384069629</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>3274.5590800539003</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>33.56465967634044</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$239,A18,'Species'!$U$2:$U$239))</x:f>
-        <x:v>109909.46111207959</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.2396876384891278</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>17.36551384069629</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>56864.40102685372</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>53045.06008522587</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.9328342359603121</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.9328342359603121</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>2031.0829645745002</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.718687487085059</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>52.32237957443491</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>2031.0829645745002</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>55.60051481240617</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$239,A19,'Species'!$U$2:$U$239))</x:f>
-        <x:v>112929.25845705034</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.718687487085059</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>52.32237957443491</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>106271.09381963554</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>6658.164637414797</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.062652640507447</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.06265264050744698</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>992.8410669933</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.19</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>154.88166189124811</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>992.8410669933</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>154.88166189124811</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$239,A20,'Species'!$U$2:$U$239))</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>153772.87444980233</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.19</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>154.88166189124811</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
-        <x:v>153772.87444980233</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>2304.3548262535</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.1371009139348036</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>137.12003452692457</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>2304.3548262535</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>166.71475009089622</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$239,A21,'Species'!$U$2:$U$239))</x:f>
-        <x:v>384169.9389796028</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.1371009139348036</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>137.12003452692457</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>315973.2133381652</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>68196.72564143763</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.2158307184364112</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.21583071843641125</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>36632.55801300011</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.112733421720161</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>129.63832817979576</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>36632.55801300011</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>163.0197421848859</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$239,A22,'Species'!$U$2:$U$239))</x:f>
-        <x:v>5971830.162852154</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.112733421720161</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>129.63832817979576</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>4748983.577754715</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>1222846.5850974387</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.2574964863693194</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.2574964863693194</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>59.3712049118</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>2.280475954730866</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>19.075501071162535</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>59.3712049118</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>19.224630416650445</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$239,A23,'Species'!$U$2:$U$239))</x:f>
-        <x:v>1141.3894718205765</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>2.280475954730866</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>19.075501071162535</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>1132.5354828912511</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>8.853988929325396</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0078178468251804</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.007817846825180292</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>961.3566620444001</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.2909391854113097</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>195.406580728569</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>961.3566620444001</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>200.37848511798896</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$239,A24,'Species'!$U$2:$U$239))</x:f>
-        <x:v>192635.19159854337</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.2909391854113097</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>195.406580728569</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>187855.4181907267</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>4779.773407816683</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.0254438943196402</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.025443894319640295</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>118.51491055470001</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.7999999999999994</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>630.9573444801923</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>118.51491055470001</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$239,A25,'Species'!$U$2:$U$239))</x:f>
-        <x:v>74777.85324490111</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.7999999999999994</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>630.9573444801923</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>74777.85324490104</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>7.275957614183426e-11</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>9.730096945086559e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>3.2335616215</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.9698906010769526</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>933.0192433379763</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>3.2335616215</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>933.0522712771233</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$239,A26,'Species'!$U$2:$U$239))</x:f>
-        <x:v>3017.0820152551123</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.9698906010769526</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>933.0192433379763</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>3016.9752173786496</x:v>
       </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>0.10679787646267869</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.0000353989903024</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.0000353989903024367</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G26">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O26">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0fe75a8104834674"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22e5337316ef4464"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18939,7 +17525,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -19038,7 +17624,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>52717675.19812377</x:v>
+        <x:v>36169282.05065127</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -19052,7 +17638,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>52717675.198123775</x:v>
+        <x:v>40799827.85035961</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -19066,7 +17652,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>7.450580596923828e-9</x:v>
+        <x:v>-16548393.147472493</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -19080,7 +17666,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>1.4901161193847656e-8</x:v>
+        <x:v>-11917847.34776415</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -19091,9 +17677,9 @@
         <x:v>EEZ_270</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -19105,47 +17691,19 @@
         <x:v>EEZ_270</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_270</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_270</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30ae8e38faaa4d47"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R977b34aa8b844a0e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19192,7 +17750,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
